--- a/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,29; 84,62</t>
+          <t>66,88; 83,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,16; 79,5</t>
+          <t>58,13; 78,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,63; 79,53</t>
+          <t>64,88; 79,13</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,81; 81,76</t>
+          <t>65,62; 80,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,18; 79,6</t>
+          <t>63,25; 79,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,83; 79,1</t>
+          <t>66,92; 79,09</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,85; 88,98</t>
+          <t>62,37; 88,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,41; 80,83</t>
+          <t>63,44; 81,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,91; 84,9</t>
+          <t>66,07; 83,73</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,19; 86,9</t>
+          <t>72,46; 86,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,12; 82,93</t>
+          <t>65,78; 82,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,28; 82,82</t>
+          <t>72,08; 83,01</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,87; 82,41</t>
+          <t>71,67; 82,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,13; 77,15</t>
+          <t>67,77; 76,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,32; 78,33</t>
+          <t>71,32; 78,18</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>41903</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49932</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>91835</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>36687; 45963</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>41573; 56244</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81992; 100001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>64816</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>99526</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>164342</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>57608; 71027</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85774; 108342</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>149490; 176681</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>75450</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64816</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>140266</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>62315; 88869</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56696; 72432</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>125068; 158483</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>71506</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67415</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>138922</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>64478; 76832</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58972; 73918</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>128756; 148274</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>253675</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>281689</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>535363</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>237616; 272868</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>261692; 296993</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>511856; 561089</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,88; 83,78</t>
+          <t>66,7; 83,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,13; 78,64</t>
+          <t>58,54; 78,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,88; 79,13</t>
+          <t>65,35; 79,08</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,62; 80,91</t>
+          <t>64,67; 80,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,25; 79,89</t>
+          <t>62,81; 79,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,92; 79,09</t>
+          <t>67,09; 78,93</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,37; 88,94</t>
+          <t>62,35; 90,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,44; 81,05</t>
+          <t>63,52; 81,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,07; 83,73</t>
+          <t>66,68; 84,48</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,46; 86,35</t>
+          <t>73,27; 87,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,78; 82,45</t>
+          <t>65,88; 82,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,08; 83,01</t>
+          <t>72,13; 82,83</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,67; 82,3</t>
+          <t>72,36; 82,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,77; 76,91</t>
+          <t>68,07; 77,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,32; 78,18</t>
+          <t>71,16; 78,17</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36687; 45963</t>
+          <t>36589; 45964</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41573; 56244</t>
+          <t>41867; 56310</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81992; 100001</t>
+          <t>82589; 99939</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57608; 71027</t>
+          <t>56771; 70841</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85774; 108342</t>
+          <t>85176; 108408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149490; 176681</t>
+          <t>149869; 176327</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62315; 88869</t>
+          <t>62303; 90301</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56696; 72432</t>
+          <t>56769; 72465</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>125068; 158483</t>
+          <t>126225; 159916</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64478; 76832</t>
+          <t>65194; 77592</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58972; 73918</t>
+          <t>59066; 74075</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128756; 148274</t>
+          <t>128844; 147959</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>237616; 272868</t>
+          <t>239906; 273005</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>261692; 296993</t>
+          <t>262850; 297538</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>511856; 561089</t>
+          <t>510709; 560991</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,7; 83,79</t>
+          <t>58,6; 80,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,54; 78,73</t>
+          <t>66,76; 84,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,35; 79,08</t>
+          <t>65,73; 79,68</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,67; 80,7</t>
+          <t>62,27; 79,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,81; 79,94</t>
+          <t>64,84; 81,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,09; 78,93</t>
+          <t>67,36; 79,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,35; 90,38</t>
+          <t>61,69; 79,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63,52; 81,08</t>
+          <t>54,13; 74,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,68; 84,48</t>
+          <t>61,76; 75,09</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,27; 87,2</t>
+          <t>67,51; 83,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,88; 82,63</t>
+          <t>71,64; 85,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,13; 82,83</t>
+          <t>71,43; 82,67</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,36; 82,34</t>
+          <t>68,21; 77,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,07; 77,05</t>
+          <t>69,37; 77,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,16; 78,17</t>
+          <t>70,13; 76,2</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41903</t>
+          <t>47786</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49932</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91835</t>
+          <t>90052</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36589; 45964</t>
+          <t>39924; 54703</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41867; 56310</t>
+          <t>37097; 46913</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82589; 99939</t>
+          <t>81313; 98564</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>107</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99526</t>
+          <t>64158</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>164342</t>
+          <t>156785</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56771; 70841</t>
+          <t>78477; 100667</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85176; 108408</t>
+          <t>56252; 71012</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149869; 176327</t>
+          <t>143340; 168483</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75450</t>
+          <t>56993</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>46520</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140266</t>
+          <t>103513</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62303; 90301</t>
+          <t>49515; 63712</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56769; 72465</t>
+          <t>38738; 52993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126225; 159916</t>
+          <t>93776; 114014</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>100</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>71506</t>
+          <t>63332</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67415</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138922</t>
+          <t>132085</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65194; 77592</t>
+          <t>56388; 69849</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59066; 74075</t>
+          <t>62247; 74420</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>128844; 147959</t>
+          <t>121724; 140876</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>346</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>253675</t>
+          <t>260739</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>482435</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>239906; 273005</t>
+          <t>244156; 275967</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>262850; 297538</t>
+          <t>208646; 233782</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>510709; 560991</t>
+          <t>461960; 501963</t>
         </is>
       </c>
     </row>
